--- a/data/trans_orig/P16A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,47 +748,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11573</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5898</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18950</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>1,92%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11573</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6348</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20714</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>24654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464683</t>
+          <t>464648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472762</t>
+          <t>472810</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,49 +861,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>295107</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>287730</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>300782</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>98,08%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>295107</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>285966</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>300332</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>738</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756450</t>
+          <t>755803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771591</t>
+          <t>771000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20173</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354176</t>
+          <t>353771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364816</t>
+          <t>364793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337203</t>
+          <t>336957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356575</t>
+          <t>356716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>696640</t>
+          <t>696730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718626</t>
+          <t>718449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38050</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519090</t>
+          <t>519945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534751</t>
+          <t>535290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147683</t>
+          <t>146633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161397</t>
+          <t>160930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672121</t>
+          <t>671669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692990</t>
+          <t>693034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57899</t>
+          <t>59407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56016</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87596</t>
+          <t>86536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1201969</t>
+          <t>1202015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1222136</t>
+          <t>1221247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656386</t>
+          <t>654878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681835</t>
+          <t>681560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1865024</t>
+          <t>1866084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1896604</t>
+          <t>1898512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>34778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59382</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43763</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73809</t>
+          <t>74004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328008</t>
+          <t>328730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342790</t>
+          <t>342536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>509370</t>
+          <t>507937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535525</t>
+          <t>533974</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>844480</t>
+          <t>844285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>874526</t>
+          <t>872678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>63701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99579</t>
+          <t>100554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72617</t>
+          <t>72412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111600</t>
+          <t>107765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280309</t>
+          <t>279963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293604</t>
+          <t>293502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1149181</t>
+          <t>1148206</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1184997</t>
+          <t>1185059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1435360</t>
+          <t>1439195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1474343</t>
+          <t>1474548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55240</t>
+          <t>55957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87257</t>
+          <t>86841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>190073</t>
+          <t>190065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>248465</t>
+          <t>248046</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>254426</t>
+          <t>256980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>322310</t>
+          <t>325746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3181915</t>
+          <t>3182331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3213932</t>
+          <t>3213215</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3129659</t>
+          <t>3130078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3188051</t>
+          <t>3188059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6324986</t>
+          <t>6321550</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6392870</t>
+          <t>6390316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31074</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418014</t>
+          <t>417732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433043</t>
+          <t>433104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297505</t>
+          <t>297296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310933</t>
+          <t>310828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>720591</t>
+          <t>722081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741141</t>
+          <t>741907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>40676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393764</t>
+          <t>393034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410743</t>
+          <t>410489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313197</t>
+          <t>313385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328970</t>
+          <t>329052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711422</t>
+          <t>713376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736988</t>
+          <t>737376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37154</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39101</t>
+          <t>39719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69346</t>
+          <t>68174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586822</t>
+          <t>587207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608717</t>
+          <t>608757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>221562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240571</t>
+          <t>240653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>814930</t>
+          <t>816102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>845175</t>
+          <t>844557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>57925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44648</t>
+          <t>44698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74624</t>
+          <t>75153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81517</t>
+          <t>81101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122025</t>
+          <t>120107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1099084</t>
+          <t>1099390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1127607</t>
+          <t>1126469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>692033</t>
+          <t>691504</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>722009</t>
+          <t>721959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1801948</t>
+          <t>1803866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1842456</t>
+          <t>1842872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21219</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75383</t>
+          <t>76756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114264</t>
+          <t>112480</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>89363</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127007</t>
+          <t>129535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488336</t>
+          <t>488685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501834</t>
+          <t>502657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>645041</t>
+          <t>646825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>683922</t>
+          <t>682549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1141853</t>
+          <t>1139325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1180863</t>
+          <t>1179497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78263</t>
+          <t>78299</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117468</t>
+          <t>116783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>78385</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117768</t>
+          <t>117696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261375</t>
+          <t>259794</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>985775</t>
+          <t>986460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1024980</t>
+          <t>1024944</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1251316</t>
+          <t>1251388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1289274</t>
+          <t>1290699</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86605</t>
+          <t>84375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126874</t>
+          <t>129616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>261505</t>
+          <t>264337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>329893</t>
+          <t>328917</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>358980</t>
+          <t>363943</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>440735</t>
+          <t>445727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3286404</t>
+          <t>3283662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3326673</t>
+          <t>3328903</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3208738</t>
+          <t>3209714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3277126</t>
+          <t>3274294</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6511174</t>
+          <t>6506182</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6592929</t>
+          <t>6587966</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31688</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418258</t>
+          <t>419017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427178</t>
+          <t>427222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324236</t>
+          <t>323592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339888</t>
+          <t>339681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>744459</t>
+          <t>747326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>764846</t>
+          <t>764890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365593</t>
+          <t>366287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375279</t>
+          <t>375252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351811</t>
+          <t>352568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366427</t>
+          <t>367316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723750</t>
+          <t>724003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740787</t>
+          <t>740430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>23444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>496969</t>
+          <t>497998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512976</t>
+          <t>513454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137934</t>
+          <t>137942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154806</t>
+          <t>155260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641179</t>
+          <t>639662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665242</t>
+          <t>664592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31190</t>
+          <t>31194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>57983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57834</t>
+          <t>55700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92747</t>
+          <t>89762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1109012</t>
+          <t>1107879</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1130462</t>
+          <t>1130305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>767274</t>
+          <t>767893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>794686</t>
+          <t>794682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1882767</t>
+          <t>1885752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917680</t>
+          <t>1919814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66191</t>
+          <t>65296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103698</t>
+          <t>101050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79607</t>
+          <t>81029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121246</t>
+          <t>121228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>594347</t>
+          <t>594066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>610795</t>
+          <t>610799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634546</t>
+          <t>637194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>672053</t>
+          <t>672948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1237704</t>
+          <t>1237722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1279343</t>
+          <t>1277921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66174</t>
+          <t>67264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102576</t>
+          <t>103602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68559</t>
+          <t>70852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105366</t>
+          <t>107887</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279092</t>
+          <t>277780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286203</t>
+          <t>286187</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>979449</t>
+          <t>978423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1015851</t>
+          <t>1014761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1263804</t>
+          <t>1261283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1300611</t>
+          <t>1298318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59043</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93699</t>
+          <t>94561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218169</t>
+          <t>223038</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284321</t>
+          <t>284443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289480</t>
+          <t>290015</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>364916</t>
+          <t>366580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3292023</t>
+          <t>3291161</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3326679</t>
+          <t>3326730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3247275</t>
+          <t>3247153</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3313427</t>
+          <t>3308558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6552402</t>
+          <t>6550738</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6627838</t>
+          <t>6627303</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>28269</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24233</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>46600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482534</t>
+          <t>482714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496721</t>
+          <t>497260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419438</t>
+          <t>419198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>434557</t>
+          <t>433959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>908241</t>
+          <t>906079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928446</t>
+          <t>928297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30374</t>
+          <t>30725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46132</t>
+          <t>46461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430408</t>
+          <t>429822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445181</t>
+          <t>444631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352206</t>
+          <t>351855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366777</t>
+          <t>366239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>788661</t>
+          <t>788332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>808898</t>
+          <t>808890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>39693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14651</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57623</t>
+          <t>56748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630368</t>
+          <t>628571</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662169</t>
+          <t>662366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145030</t>
+          <t>144504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156319</t>
+          <t>155959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>777552</t>
+          <t>778427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820524</t>
+          <t>818793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28237</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51440</t>
+          <t>51178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>31678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83924</t>
+          <t>84558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69997</t>
+          <t>67771</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122360</t>
+          <t>119699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>983379</t>
+          <t>983641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1006582</t>
+          <t>1006858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>893273</t>
+          <t>892639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946415</t>
+          <t>945519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889656</t>
+          <t>1892317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1942019</t>
+          <t>1944245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29537</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>57175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92443</t>
+          <t>94321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79328</t>
+          <t>77855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114660</t>
+          <t>115133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444022</t>
+          <t>444713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461378</t>
+          <t>461018</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>746553</t>
+          <t>744675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>783780</t>
+          <t>781821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1197895</t>
+          <t>1197422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1233227</t>
+          <t>1234700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12140</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49598</t>
+          <t>49001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73979</t>
+          <t>73651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>51512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78641</t>
+          <t>78870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228367</t>
+          <t>228617</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238962</t>
+          <t>238973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>686173</t>
+          <t>686501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>710554</t>
+          <t>711151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>922018</t>
+          <t>921789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>948734</t>
+          <t>949147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83690</t>
+          <t>84958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134917</t>
+          <t>131830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>212498</t>
+          <t>209944</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287164</t>
+          <t>286415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310369</t>
+          <t>312143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>403333</t>
+          <t>407721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3239657</t>
+          <t>3242744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3290884</t>
+          <t>3289616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3286139</t>
+          <t>3286888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3360805</t>
+          <t>3363359</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6544544</t>
+          <t>6540156</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6637508</t>
+          <t>6635734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,47 +748,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11573</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19577</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11573</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5898</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18950</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24654</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464648</t>
+          <t>465215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472810</t>
+          <t>472910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,49 +861,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>295107</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>287103</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,62%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>98,07%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>295107</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>287730</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>300782</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>738</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755803</t>
+          <t>755069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>771000</t>
+          <t>771161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>34752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42069</t>
+          <t>41471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353771</t>
+          <t>354241</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364793</t>
+          <t>364775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336957</t>
+          <t>337113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356716</t>
+          <t>356334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>696730</t>
+          <t>697328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718449</t>
+          <t>719072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>38074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519945</t>
+          <t>520227</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535290</t>
+          <t>534405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146633</t>
+          <t>146303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160930</t>
+          <t>161185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671669</t>
+          <t>672097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>693034</t>
+          <t>691701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59407</t>
+          <t>59913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54108</t>
+          <t>53407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86536</t>
+          <t>87651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1202015</t>
+          <t>1201856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1221247</t>
+          <t>1221246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654878</t>
+          <t>654372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681560</t>
+          <t>680807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1866084</t>
+          <t>1864969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898512</t>
+          <t>1899213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34778</t>
+          <t>34324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60815</t>
+          <t>61624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45611</t>
+          <t>44582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74004</t>
+          <t>74554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328730</t>
+          <t>328927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342536</t>
+          <t>343156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507937</t>
+          <t>507128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533974</t>
+          <t>534428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>844285</t>
+          <t>843735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>872678</t>
+          <t>873707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63701</t>
+          <t>64573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100554</t>
+          <t>97497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72412</t>
+          <t>72855</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107765</t>
+          <t>110035</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279963</t>
+          <t>280490</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293502</t>
+          <t>293563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1148206</t>
+          <t>1151263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1185059</t>
+          <t>1184187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1439195</t>
+          <t>1436925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1474548</t>
+          <t>1474105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55957</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86841</t>
+          <t>88781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>190065</t>
+          <t>190754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>248046</t>
+          <t>246725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>256980</t>
+          <t>252801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325746</t>
+          <t>321087</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3182331</t>
+          <t>3180391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3213215</t>
+          <t>3213195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3130078</t>
+          <t>3131399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3188059</t>
+          <t>3187370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6321550</t>
+          <t>6326209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6390316</t>
+          <t>6394495</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>29769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417732</t>
+          <t>417658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433104</t>
+          <t>433018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297296</t>
+          <t>297080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310828</t>
+          <t>310684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>722081</t>
+          <t>721896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741907</t>
+          <t>741145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40676</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393034</t>
+          <t>392937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410489</t>
+          <t>410900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313385</t>
+          <t>313938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329052</t>
+          <t>329499</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713376</t>
+          <t>714162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737376</t>
+          <t>737471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>39797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>36358</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39719</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68174</t>
+          <t>67634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>587207</t>
+          <t>586541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608757</t>
+          <t>609110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221562</t>
+          <t>221580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240653</t>
+          <t>240853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>816102</t>
+          <t>816642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>844557</t>
+          <t>845461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30846</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>58127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44698</t>
+          <t>45289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75153</t>
+          <t>74994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81101</t>
+          <t>81144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120107</t>
+          <t>121583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1099390</t>
+          <t>1099188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1126469</t>
+          <t>1126903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>691504</t>
+          <t>691663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721959</t>
+          <t>721368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1803866</t>
+          <t>1802390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1842872</t>
+          <t>1842829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76756</t>
+          <t>76155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112480</t>
+          <t>115094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89363</t>
+          <t>90076</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129535</t>
+          <t>128974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488685</t>
+          <t>488646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502657</t>
+          <t>502604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>646825</t>
+          <t>644211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682549</t>
+          <t>683150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1139325</t>
+          <t>1139886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1179497</t>
+          <t>1178784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78299</t>
+          <t>77242</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116783</t>
+          <t>115404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78385</t>
+          <t>78700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117696</t>
+          <t>116357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259794</t>
+          <t>260930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>986460</t>
+          <t>987839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1024944</t>
+          <t>1026001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1251388</t>
+          <t>1252727</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1290699</t>
+          <t>1290384</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84375</t>
+          <t>82389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129616</t>
+          <t>129228</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>264337</t>
+          <t>263493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>328917</t>
+          <t>329073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>363943</t>
+          <t>362278</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>445727</t>
+          <t>446803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3283662</t>
+          <t>3284050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3328903</t>
+          <t>3330889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3209714</t>
+          <t>3209558</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3274294</t>
+          <t>3275138</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6506182</t>
+          <t>6505106</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6587966</t>
+          <t>6589631</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>28845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419017</t>
+          <t>417365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427222</t>
+          <t>427172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323592</t>
+          <t>324294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339681</t>
+          <t>340047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>747326</t>
+          <t>747302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>764890</t>
+          <t>765149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366287</t>
+          <t>366388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375252</t>
+          <t>375327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352568</t>
+          <t>352983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367316</t>
+          <t>366606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724003</t>
+          <t>723442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740430</t>
+          <t>740413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>25387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>27613</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23444</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48374</t>
+          <t>48999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497998</t>
+          <t>496527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513454</t>
+          <t>512868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>138510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155260</t>
+          <t>155465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639662</t>
+          <t>639037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664592</t>
+          <t>664665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19333</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41759</t>
+          <t>41652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31194</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57983</t>
+          <t>58257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55700</t>
+          <t>56443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89762</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1107879</t>
+          <t>1107986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1130305</t>
+          <t>1130398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>767893</t>
+          <t>767619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>794682</t>
+          <t>793245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885752</t>
+          <t>1885265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1919814</t>
+          <t>1919071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>67140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101050</t>
+          <t>99521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81029</t>
+          <t>81531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121228</t>
+          <t>120338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>594066</t>
+          <t>594610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>610799</t>
+          <t>610709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>637194</t>
+          <t>638723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>672948</t>
+          <t>671104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1237722</t>
+          <t>1238612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1277921</t>
+          <t>1277419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67264</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103602</t>
+          <t>102244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70852</t>
+          <t>69220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107887</t>
+          <t>108979</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277780</t>
+          <t>278697</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286187</t>
+          <t>286196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>978423</t>
+          <t>979781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1014761</t>
+          <t>1017611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1261283</t>
+          <t>1260191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1298318</t>
+          <t>1299950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58992</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94561</t>
+          <t>94813</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223038</t>
+          <t>221739</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284443</t>
+          <t>283425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>290015</t>
+          <t>289185</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>366580</t>
+          <t>366007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3291161</t>
+          <t>3290909</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3326730</t>
+          <t>3326259</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3247153</t>
+          <t>3248171</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3308558</t>
+          <t>3309857</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6550738</t>
+          <t>6551311</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6627303</t>
+          <t>6628133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28269</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>35759</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46600</t>
+          <t>47590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>491347</t>
+          <t>536209</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482714</t>
+          <t>525736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>497260</t>
+          <t>542030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>427989</t>
+          <t>467061</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419198</t>
+          <t>457641</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433959</t>
+          <t>473332</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>919336</t>
+          <t>1003270</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906079</t>
+          <t>991439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928297</t>
+          <t>1013492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>51551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>439406</t>
+          <t>469637</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429822</t>
+          <t>460919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>444631</t>
+          <t>475570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>360237</t>
+          <t>398509</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351855</t>
+          <t>389881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366239</t>
+          <t>405248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>799643</t>
+          <t>868147</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>788332</t>
+          <t>854804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>808890</t>
+          <t>877749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20937</t>
+          <t>21686</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>32247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>36478</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56748</t>
+          <t>49559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>647327</t>
+          <t>449926</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628571</t>
+          <t>439365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662366</t>
+          <t>458299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151370</t>
+          <t>171187</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144504</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155959</t>
+          <t>176896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>798697</t>
+          <t>621113</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>778427</t>
+          <t>609550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818793</t>
+          <t>631376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37884</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27961</t>
+          <t>32002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>56243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>68931</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31678</t>
+          <t>56538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84558</t>
+          <t>83972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>100157</t>
+          <t>111463</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67771</t>
+          <t>93486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119699</t>
+          <t>131766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>996935</t>
+          <t>1089311</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>983641</t>
+          <t>1075600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1006858</t>
+          <t>1099841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>914925</t>
+          <t>791353</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>892639</t>
+          <t>776312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>945519</t>
+          <t>803746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1911859</t>
+          <t>1880664</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892317</t>
+          <t>1860361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1944245</t>
+          <t>1898641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>76747</t>
+          <t>84149</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57175</t>
+          <t>70861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94321</t>
+          <t>99470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>96317</t>
+          <t>105265</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77855</t>
+          <t>88091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115133</t>
+          <t>120810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>453989</t>
+          <t>545365</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444713</t>
+          <t>534180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461018</t>
+          <t>552507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>762249</t>
+          <t>745978</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744675</t>
+          <t>730657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>781821</t>
+          <t>759266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1216238</t>
+          <t>1291343</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1197422</t>
+          <t>1275798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1234700</t>
+          <t>1308517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59556</t>
+          <t>64199</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49001</t>
+          <t>53010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73651</t>
+          <t>77970</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>64226</t>
+          <t>70600</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51512</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78870</t>
+          <t>85720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235836</t>
+          <t>230827</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228617</t>
+          <t>222231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238973</t>
+          <t>234881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>700596</t>
+          <t>778794</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>686501</t>
+          <t>765023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>711151</t>
+          <t>789983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>936433</t>
+          <t>1009621</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>921789</t>
+          <t>994501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>949147</t>
+          <t>1023583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>119719</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84958</t>
+          <t>97856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131830</t>
+          <t>142264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>255937</t>
+          <t>279573</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209944</t>
+          <t>254424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>286415</t>
+          <t>304508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>365672</t>
+          <t>399292</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>312143</t>
+          <t>364728</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407721</t>
+          <t>434831</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3264839</t>
+          <t>3321274</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3242744</t>
+          <t>3298729</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3289616</t>
+          <t>3343137</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3317366</t>
+          <t>3352882</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3286888</t>
+          <t>3327947</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3363359</t>
+          <t>3378031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6582205</t>
+          <t>6674157</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6540156</t>
+          <t>6638618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6635734</t>
+          <t>6708721</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
